--- a/docs/Sensor_Inventory.xlsx
+++ b/docs/Sensor_Inventory.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mysait-my.sharepoint.com/personal/suhavikaur_edu_sait_ca/Documents/Capstone_Project/DSM_project/docs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mrico\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="99" documentId="11_EDB3F2227B97E4CE9F476517B4EB3C0379F181C1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6FB03A7-0E73-4B00-829C-8F2CC6E898A6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D78AE15B-A53A-45A4-A30A-6084CA9D7972}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28050" yWindow="17880" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="614" uniqueCount="411">
   <si>
     <t>Trend Column</t>
   </si>
@@ -1233,6 +1233,27 @@
   </si>
   <si>
     <t>Solar generation</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Wh</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>kWh</t>
+  </si>
+  <si>
+    <t>Celsius</t>
+  </si>
+  <si>
+    <t>PPM</t>
+  </si>
+  <si>
+    <t>cubic meters per hour</t>
   </si>
 </sst>
 </file>
@@ -1331,7 +1352,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1345,6 +1366,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1649,16 +1673,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G125"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.109375" customWidth="1"/>
-    <col min="2" max="2" width="18.77734375" customWidth="1"/>
-    <col min="3" max="3" width="24.44140625" customWidth="1"/>
-    <col min="4" max="4" width="21.44140625" customWidth="1"/>
-    <col min="5" max="5" width="16.33203125" customWidth="1"/>
+    <col min="1" max="1" width="24.08984375" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" customWidth="1"/>
+    <col min="3" max="3" width="24.453125" customWidth="1"/>
+    <col min="4" max="4" width="21.453125" customWidth="1"/>
+    <col min="5" max="5" width="16.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1681,7 +1705,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1704,7 +1728,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>70</v>
       </c>
@@ -1718,7 +1742,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>73</v>
       </c>
@@ -1738,7 +1762,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -1758,7 +1782,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>77</v>
       </c>
@@ -1778,7 +1802,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>79</v>
       </c>
@@ -1798,7 +1822,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>81</v>
       </c>
@@ -1818,7 +1842,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>83</v>
       </c>
@@ -1838,7 +1862,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>85</v>
       </c>
@@ -1858,7 +1882,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>87</v>
       </c>
@@ -1878,7 +1902,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>89</v>
       </c>
@@ -1898,7 +1922,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>91</v>
       </c>
@@ -1918,7 +1942,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>93</v>
       </c>
@@ -1938,7 +1962,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>95</v>
       </c>
@@ -1958,7 +1982,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>97</v>
       </c>
@@ -1978,7 +2002,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>99</v>
       </c>
@@ -1998,7 +2022,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>13</v>
       </c>
@@ -2021,7 +2045,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>101</v>
       </c>
@@ -2035,7 +2059,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>104</v>
       </c>
@@ -2049,7 +2073,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>107</v>
       </c>
@@ -2063,7 +2087,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>110</v>
       </c>
@@ -2077,7 +2101,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>113</v>
       </c>
@@ -2091,7 +2115,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>116</v>
       </c>
@@ -2105,7 +2129,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>118</v>
       </c>
@@ -2119,7 +2143,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>121</v>
       </c>
@@ -2133,7 +2157,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>124</v>
       </c>
@@ -2147,7 +2171,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>127</v>
       </c>
@@ -2161,7 +2185,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>130</v>
       </c>
@@ -2175,7 +2199,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>133</v>
       </c>
@@ -2189,7 +2213,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>136</v>
       </c>
@@ -2203,7 +2227,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -2226,7 +2250,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>21</v>
       </c>
@@ -2249,7 +2273,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>25</v>
       </c>
@@ -2272,7 +2296,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>139</v>
       </c>
@@ -2286,7 +2310,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>29</v>
       </c>
@@ -2309,7 +2333,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>33</v>
       </c>
@@ -2332,7 +2356,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>142</v>
       </c>
@@ -2355,7 +2379,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>37</v>
       </c>
@@ -2375,7 +2399,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>146</v>
       </c>
@@ -2389,7 +2413,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>149</v>
       </c>
@@ -2403,7 +2427,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>152</v>
       </c>
@@ -2417,7 +2441,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>155</v>
       </c>
@@ -2431,7 +2455,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>40</v>
       </c>
@@ -2451,7 +2475,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>43</v>
       </c>
@@ -2471,7 +2495,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>158</v>
       </c>
@@ -2485,7 +2509,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>161</v>
       </c>
@@ -2499,7 +2523,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>164</v>
       </c>
@@ -2513,7 +2537,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>167</v>
       </c>
@@ -2527,7 +2551,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>46</v>
       </c>
@@ -2547,7 +2571,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>170</v>
       </c>
@@ -2561,7 +2585,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>173</v>
       </c>
@@ -2575,7 +2599,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>176</v>
       </c>
@@ -2589,7 +2613,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>179</v>
       </c>
@@ -2603,7 +2627,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>49</v>
       </c>
@@ -2623,7 +2647,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>182</v>
       </c>
@@ -2637,7 +2661,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>185</v>
       </c>
@@ -2651,7 +2675,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>188</v>
       </c>
@@ -2665,7 +2689,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>191</v>
       </c>
@@ -2679,7 +2703,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>194</v>
       </c>
@@ -2693,7 +2717,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>197</v>
       </c>
@@ -2707,7 +2731,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>200</v>
       </c>
@@ -2721,7 +2745,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>52</v>
       </c>
@@ -2741,7 +2765,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>55</v>
       </c>
@@ -2761,7 +2785,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>58</v>
       </c>
@@ -2781,7 +2805,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>61</v>
       </c>
@@ -2801,7 +2825,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>203</v>
       </c>
@@ -2815,7 +2839,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>206</v>
       </c>
@@ -2829,7 +2853,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>209</v>
       </c>
@@ -2843,7 +2867,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>212</v>
       </c>
@@ -2857,7 +2881,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>64</v>
       </c>
@@ -2877,7 +2901,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>215</v>
       </c>
@@ -2891,7 +2915,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>67</v>
       </c>
@@ -2914,7 +2938,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>218</v>
       </c>
@@ -2928,7 +2952,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>221</v>
       </c>
@@ -2942,7 +2966,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>224</v>
       </c>
@@ -2956,7 +2980,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>227</v>
       </c>
@@ -2970,7 +2994,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>230</v>
       </c>
@@ -2984,7 +3008,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>233</v>
       </c>
@@ -2998,7 +3022,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>236</v>
       </c>
@@ -3012,7 +3036,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>239</v>
       </c>
@@ -3026,7 +3050,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>242</v>
       </c>
@@ -3040,7 +3064,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>245</v>
       </c>
@@ -3054,7 +3078,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>248</v>
       </c>
@@ -3068,7 +3092,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>251</v>
       </c>
@@ -3082,7 +3106,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>254</v>
       </c>
@@ -3096,7 +3120,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>257</v>
       </c>
@@ -3110,7 +3134,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>260</v>
       </c>
@@ -3124,7 +3148,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>263</v>
       </c>
@@ -3138,7 +3162,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>266</v>
       </c>
@@ -3152,7 +3176,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>269</v>
       </c>
@@ -3166,7 +3190,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>272</v>
       </c>
@@ -3180,7 +3204,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>275</v>
       </c>
@@ -3194,7 +3218,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>278</v>
       </c>
@@ -3208,7 +3232,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>281</v>
       </c>
@@ -3222,7 +3246,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>284</v>
       </c>
@@ -3236,7 +3260,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>287</v>
       </c>
@@ -3250,7 +3274,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>290</v>
       </c>
@@ -3264,7 +3288,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>293</v>
       </c>
@@ -3278,7 +3302,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>296</v>
       </c>
@@ -3292,7 +3316,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>299</v>
       </c>
@@ -3306,7 +3330,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>302</v>
       </c>
@@ -3320,7 +3344,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>305</v>
       </c>
@@ -3334,7 +3358,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>308</v>
       </c>
@@ -3348,7 +3372,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>311</v>
       </c>
@@ -3362,7 +3386,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>314</v>
       </c>
@@ -3376,7 +3400,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>317</v>
       </c>
@@ -3390,7 +3414,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>320</v>
       </c>
@@ -3404,7 +3428,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>323</v>
       </c>
@@ -3418,7 +3442,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>326</v>
       </c>
@@ -3432,7 +3456,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>329</v>
       </c>
@@ -3446,7 +3470,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>332</v>
       </c>
@@ -3460,7 +3484,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>335</v>
       </c>
@@ -3474,7 +3498,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>338</v>
       </c>
@@ -3488,7 +3512,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>341</v>
       </c>
@@ -3502,7 +3526,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>344</v>
       </c>
@@ -3516,7 +3540,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>347</v>
       </c>
@@ -3530,7 +3554,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>350</v>
       </c>
@@ -3544,7 +3568,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>353</v>
       </c>
@@ -3558,7 +3582,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>356</v>
       </c>
@@ -3572,7 +3596,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>359</v>
       </c>
@@ -3586,7 +3610,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>362</v>
       </c>
@@ -3600,7 +3624,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>365</v>
       </c>
@@ -3614,7 +3638,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>368</v>
       </c>
@@ -3628,7 +3652,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>371</v>
       </c>
@@ -3650,19 +3674,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="26.21875" customWidth="1"/>
-    <col min="2" max="2" width="21.21875" customWidth="1"/>
-    <col min="3" max="3" width="36.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.109375" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" customWidth="1"/>
-    <col min="6" max="6" width="12.6640625" customWidth="1"/>
-    <col min="7" max="7" width="23.21875" customWidth="1"/>
-    <col min="8" max="8" width="21.21875" customWidth="1"/>
+    <col min="1" max="1" width="26.1796875" customWidth="1"/>
+    <col min="2" max="2" width="21.1796875" customWidth="1"/>
+    <col min="3" max="3" width="36.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.08984375" customWidth="1"/>
+    <col min="5" max="5" width="20.6328125" customWidth="1"/>
+    <col min="6" max="6" width="12.6328125" customWidth="1"/>
+    <col min="7" max="7" width="23.1796875" customWidth="1"/>
+    <col min="8" max="8" width="21.1796875" customWidth="1"/>
+    <col min="9" max="9" width="19.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3687,8 +3712,11 @@
       <c r="H1" s="4" t="s">
         <v>375</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I1" s="6" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>142</v>
       </c>
@@ -3713,8 +3741,11 @@
       <c r="H2" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I2" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -3740,7 +3771,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>46</v>
       </c>
@@ -3765,8 +3796,11 @@
       <c r="H4" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I4" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>49</v>
       </c>
@@ -3791,8 +3825,11 @@
       <c r="H5" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I5" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>52</v>
       </c>
@@ -3817,10 +3854,12 @@
       <c r="H6" t="s">
         <v>402</v>
       </c>
-      <c r="I6" s="5"/>
+      <c r="I6" s="5" t="s">
+        <v>406</v>
+      </c>
       <c r="J6" s="5"/>
     </row>
-    <row r="7" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>64</v>
       </c>
@@ -3845,8 +3884,11 @@
       <c r="H7" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I7" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -3871,8 +3913,11 @@
       <c r="H8" t="s">
         <v>402</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I8" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -3897,8 +3942,11 @@
       <c r="H9" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I9" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>67</v>
       </c>
@@ -3923,8 +3971,11 @@
       <c r="H10" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I10" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>25</v>
       </c>
@@ -3949,8 +4000,11 @@
       <c r="H11" t="s">
         <v>401</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I11" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>40</v>
       </c>
@@ -3975,8 +4029,11 @@
       <c r="H12" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I12" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>43</v>
       </c>
@@ -4001,8 +4058,11 @@
       <c r="H13" t="s">
         <v>403</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I13" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -4027,8 +4087,11 @@
       <c r="H14" t="s">
         <v>400</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I14" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -4053,8 +4116,11 @@
       <c r="H15" t="s">
         <v>399</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="I15" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -4079,8 +4145,11 @@
       <c r="H16" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I16" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -4105,8 +4174,11 @@
       <c r="H17" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I17" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -4131,8 +4203,11 @@
       <c r="H18" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I18" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>61</v>
       </c>
@@ -4157,8 +4232,11 @@
       <c r="H19" t="s">
         <v>398</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="I19" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -4182,6 +4260,9 @@
       </c>
       <c r="H20" t="s">
         <v>399</v>
+      </c>
+      <c r="I20" t="s">
+        <v>408</v>
       </c>
     </row>
   </sheetData>
